--- a/CAXE_Banque_Questions.xlsx
+++ b/CAXE_Banque_Questions.xlsx
@@ -22011,7 +22011,7 @@
       </c>
       <c r="P304" s="6" t="inlineStr">
         <is>
-          <t>Prix ou devis · Question d'un client · Fournisseur · Planning · Manière de faire · Problème technique</t>
+          <t>Prix ou devis · Question d'un client · Fournisseur · Planning · Manière de faire · Problème technique · Aucune demande de ce type</t>
         </is>
       </c>
       <c r="Q304" s="7" t="n"/>
@@ -24107,7 +24107,7 @@
       </c>
       <c r="P335" s="6" t="inlineStr">
         <is>
-          <t>Demande client de dernière minute · Erreur ou oubli interne · Retard fournisseur · Panne ou incident · Manque de planification · Absence imprévue</t>
+          <t>Demande client de dernière minute · Erreur ou oubli interne · Retard fournisseur · Panne ou incident · Manque de planification · Absence imprévue · Aucune urgence de ce type</t>
         </is>
       </c>
       <c r="Q335" s="7" t="n"/>
@@ -31261,7 +31261,7 @@
       <c r="O439" s="7" t="n"/>
       <c r="P439" s="6" t="inlineStr">
         <is>
-          <t>LinkedIn · Instagram · Facebook · TikTok · YouTube · Pinterest · X</t>
+          <t>LinkedIn · Instagram · Facebook · TikTok · YouTube · Pinterest · X · Aucun</t>
         </is>
       </c>
       <c r="Q439" s="7" t="n"/>
@@ -36883,7 +36883,7 @@
       </c>
       <c r="P517" s="6" t="inlineStr">
         <is>
-          <t>Le manque de temps · Le manque d'idées · Ne pas savoir quoi montrer · Ne pas aimer se montrer · Ne pas savoir s'y prendre · Douter que cela amène des clients</t>
+          <t>Le manque de temps · Le manque d'idées · Ne pas savoir quoi montrer · Ne pas aimer se montrer · Ne pas savoir s'y prendre · Douter que cela amène des clients · Rien de particulier</t>
         </is>
       </c>
       <c r="Q517" s="7" t="n"/>
@@ -40950,7 +40950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -40975,23 +40975,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>D20</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Jours d'ouverture</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Lundi · Mardi · Mercredi · Jeudi · Vendredi · Samedi · Dimanche</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CAXE_Banque_Questions.xlsx
+++ b/CAXE_Banque_Questions.xlsx
@@ -754,7 +754,7 @@
       </c>
       <c r="S1" s="4" t="inlineStr">
         <is>
-          <t>Total imposé (Colonne = valeur)</t>
+          <t>Total imposé (Colonne = valeur ; plusieurs colonnes séparées par « ; »)</t>
         </is>
       </c>
       <c r="T1" s="3" t="inlineStr">
@@ -870,7 +870,7 @@
       <c r="H3" s="5" t="n"/>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>Quelle part de votre chiffre d'affaires vient de chacune de ces catégories de clients ?</t>
+          <t>Sur les 12 derniers mois, quelle part de votre chiffre d'affaires vient de chacune de ces catégories de clients ?</t>
         </is>
       </c>
       <c r="J3" s="6" t="inlineStr">
@@ -968,7 +968,7 @@
       <c r="P4" s="7" t="n"/>
       <c r="Q4" s="6" t="inlineStr">
         <is>
-          <t>Clients sur 12 mois [nombre]</t>
+          <t>Clients sur 12 mois [nombre 0-]</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
@@ -1042,7 +1042,7 @@
       <c r="P5" s="7" t="n"/>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>Fois par an [nombre]</t>
+          <t>Fois par an [nombre 0-]</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
@@ -1170,7 +1170,7 @@
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>À quelle distance de votre entreprise se trouvent vos clients ?</t>
+          <t>Sur les 12 derniers mois, à quelle distance de votre entreprise se trouvaient vos clients ?</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
@@ -1312,7 +1312,7 @@
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>Quelle part de votre chiffre d'affaires faites-vous dans cette zone ?</t>
+          <t>Sur les 12 derniers mois, quelle part de votre chiffre d'affaires avez-vous faite dans cette zone ?</t>
         </is>
       </c>
       <c r="J9" s="7" t="n"/>
@@ -1446,7 +1446,7 @@
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>Quelle part de vos ventes se fait hors de votre région, y compris à l'étranger ?</t>
+          <t>Sur les 12 derniers mois, quelle part de vos commandes vient de clients situés hors de votre région, y compris à l'étranger ?</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>Cochez tous ceux qui vous ont amené au moins un client. Bouche-à-oreille : vos clients et votre entourage. Partenaires : des professionnels qui vous recommandent. Réseaux sociaux : vos publications ; leur publicité payante va dans Publicité en ligne. Emailing et SMS : vos messages à vos propres contacts ; à des inconnus, c'est de la Prospection. Plateformes : TheFork, Doctolib, Booking, Uber Eats, Malt, marketplace… Annuaires : PagesJaunes et sites d'annuaires. Réseaux d'affaires : BNI, CCI, clubs d'entrepreneurs. Réseau ou enseigne : les clients envoyés par votre franchise ou votre groupement. Passage : les clients qui passent devant chez vous.</t>
+          <t>Cochez tous ceux qui vous ont amené au moins un client : chaque canal coché ouvre ensuite quelques questions sur lui (part des demandes, des nouveaux clients, du chiffre d'affaires). Bouche-à-oreille : vos clients et votre entourage. Partenaires : des professionnels qui vous recommandent. Réseaux sociaux : vos publications ; leur publicité payante va dans Publicité en ligne. Emailing et SMS : vos messages à vos propres contacts ; à des inconnus, c'est de la Prospection. Plateformes : TheFork, Doctolib, Booking, Uber Eats, Malt, marketplace… Annuaires : PagesJaunes et sites d'annuaires. Réseaux d'affaires : BNI, CCI, clubs d'entrepreneurs. Réseau ou enseigne : les clients envoyés par votre franchise ou votre groupement. Passage : les clients qui passent devant chez vous.</t>
         </is>
       </c>
       <c r="K17" s="7" t="n"/>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>Quelle part de vos {demandes} vient de chaque canal ?</t>
+          <t>Sur les 12 derniers mois, quelle part de vos {demandes} est arrivée par chaque canal ?</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>Par exemple : 50 % bouche-à-oreille, 30 % fiche Google, 20 % site internet. Une estimation suffit.</t>
+          <t>Une demande compte dans un seul canal : celui par lequel elle vous est arrivée. Par exemple : 50 % bouche-à-oreille, 30 % fiche Google, 20 % site internet. Une estimation suffit.</t>
         </is>
       </c>
       <c r="K18" s="7" t="n"/>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>Quelle part de vos nouveaux clients vient de chaque canal ?</t>
+          <t>Sur les 12 derniers mois, quelle part de vos nouveaux clients est arrivée par chaque canal ?</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
@@ -2420,7 +2420,7 @@
       <c r="P24" s="7" t="n"/>
       <c r="Q24" s="6" t="inlineStr">
         <is>
-          <t>Par semaine [nombre]</t>
+          <t>Par semaine [nombre 0-]</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
@@ -2926,7 +2926,7 @@
       <c r="P31" s="7" t="n"/>
       <c r="Q31" s="6" t="inlineStr">
         <is>
-          <t>Contacts apportés par mois (moyenne des 3 derniers mois) [nombre] · Nouveaux clients sur 12 mois [nombre] · Chiffre d'affaires sur 12 mois [€ 0-]</t>
+          <t>Contacts apportés par mois (moyenne des 3 derniers mois) [nombre 0-] · Nouveaux clients sur 12 mois [nombre 0-] · Chiffre d'affaires sur 12 mois [€ 0-]</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
@@ -3078,7 +3078,7 @@
       <c r="P33" s="7" t="n"/>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>Avis au total [nombre] · Note sur 5 [nombre 0-5] · Avis reçus sur les 6 derniers mois [nombre]</t>
+          <t>Avis au total [nombre 0-] · Note sur 5 [nombre 0-5] · Avis reçus sur les 6 derniers mois [nombre 0-]</t>
         </is>
       </c>
       <c r="R33" s="7" t="n"/>
@@ -3152,7 +3152,7 @@
       <c r="P34" s="7" t="n"/>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>Vues de votre fiche [nombre] · Appels [nombre] · Demandes d'itinéraire [nombre] · Clics vers votre site [nombre]</t>
+          <t>Vues de votre fiche [nombre 0-] · Appels [nombre 0-] · Demandes d'itinéraire [nombre 0-] · Clics vers votre site [nombre 0-]</t>
         </is>
       </c>
       <c r="R34" s="7" t="n"/>
@@ -3226,7 +3226,7 @@
       <c r="P35" s="7" t="n"/>
       <c r="Q35" s="6" t="inlineStr">
         <is>
-          <t>Nom [texte] · Avis [nombre] · Note sur 5 [nombre 0-5]</t>
+          <t>Nom [texte] · Avis [nombre 0-] · Note sur 5 [nombre 0-5]</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
@@ -3376,7 +3376,7 @@
       <c r="P37" s="7" t="n"/>
       <c r="Q37" s="6" t="inlineStr">
         <is>
-          <t>Note [nombre] · Note sur [choix: 5 / 10] · Nombre d'avis [nombre]</t>
+          <t>Note [nombre 0-] · Note sur [choix: 5 / 10] · Nombre d'avis [nombre 0-]</t>
         </is>
       </c>
       <c r="R37" s="7" t="n"/>
@@ -3526,7 +3526,7 @@
       <c r="P39" s="7" t="n"/>
       <c r="Q39" s="6" t="inlineStr">
         <is>
-          <t>Nombre de recherches [nombre]</t>
+          <t>Nombre de recherches [nombre 0-]</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>Pour chaque plateforme, quelle part de votre chiffre d'affaires vous apporte-t-elle, et quel pourcentage prélève-t-elle ?</t>
+          <t>Sur les 12 derniers mois, pour chaque plateforme : quelle part de votre chiffre d'affaires vous a-t-elle apportée, et quel pourcentage prélève-t-elle ?</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
@@ -3961,8 +3961,12 @@
           <t>%</t>
         </is>
       </c>
-      <c r="N45" s="7" t="n"/>
-      <c r="O45" s="7" t="n"/>
+      <c r="N45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="6" t="n">
+        <v>100</v>
+      </c>
       <c r="P45" s="7" t="n"/>
       <c r="Q45" s="7" t="n"/>
       <c r="R45" s="7" t="n"/>
@@ -4239,7 +4243,7 @@
       <c r="O49" s="7" t="n"/>
       <c r="P49" s="6" t="inlineStr">
         <is>
-          <t>Téléphone · Email · Formulaire du site · Messages (réseaux sociaux, WhatsApp, SMS)</t>
+          <t>Téléphone · Email · Formulaire du site · Messages (réseaux sociaux, WhatsApp, SMS) · Aucun : je réponds aussi vite partout</t>
         </is>
       </c>
       <c r="Q49" s="7" t="n"/>
@@ -4452,7 +4456,7 @@
       <c r="P52" s="7" t="n"/>
       <c r="Q52" s="6" t="inlineStr">
         <is>
-          <t>Annulés en vous prévenant [nombre] · Absents sans prévenir [nombre]</t>
+          <t>Annulés en vous prévenant [nombre 0-] · Absents sans prévenir [nombre 0-]</t>
         </is>
       </c>
       <c r="R52" s="7" t="n"/>
@@ -4742,7 +4746,7 @@
       <c r="P56" s="7" t="n"/>
       <c r="Q56" s="6" t="inlineStr">
         <is>
-          <t>Nombre par mois [nombre] · Montant total par mois [€ 0-]</t>
+          <t>Nombre par mois [nombre 0-] · Montant total par mois [€ 0-]</t>
         </is>
       </c>
       <c r="R56" s="7" t="n"/>
@@ -4816,7 +4820,7 @@
       <c r="P57" s="7" t="n"/>
       <c r="Q57" s="6" t="inlineStr">
         <is>
-          <t>Nombre par mois [nombre] · Montant total par mois [€ 0-]</t>
+          <t>Nombre par mois [nombre 0-] · Montant total par mois [€ 0-]</t>
         </is>
       </c>
       <c r="R57" s="7" t="n"/>
@@ -5104,7 +5108,7 @@
       <c r="P61" s="7" t="n"/>
       <c r="Q61" s="6" t="inlineStr">
         <is>
-          <t>Nombre [nombre] · Montant total [€ 0-]</t>
+          <t>Nombre [nombre 0-] · Montant total [€ 0-]</t>
         </is>
       </c>
       <c r="R61" s="7" t="n"/>
@@ -5567,7 +5571,7 @@
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
-          <t>Répartissez, par exemple 50 % prix, 30 % pas assez relancé, 20 % projet abandonné. Une estimation suffit.</t>
+          <t>Comptez chaque affaire perdue une fois, avec sa raison principale. Répartissez, par exemple 50 % prix, 30 % pas assez relancé, 20 % projet abandonné. Une estimation suffit.</t>
         </is>
       </c>
       <c r="K68" s="7" t="n"/>
@@ -5724,7 +5728,7 @@
       <c r="P70" s="7" t="n"/>
       <c r="Q70" s="6" t="inlineStr">
         <is>
-          <t>Couverts par service [nombre]</t>
+          <t>Couverts par service [nombre 0-]</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr">
@@ -6116,7 +6120,7 @@
       <c r="H76" s="5" t="n"/>
       <c r="I76" s="6" t="inlineStr">
         <is>
-          <t>Quelle part de votre chiffre d'affaires vient de la vente à emporter et de la livraison ?</t>
+          <t>Sur les 12 derniers mois, quelle part de votre chiffre d'affaires vient de la vente à emporter et de la livraison ?</t>
         </is>
       </c>
       <c r="J76" s="7" t="n"/>
@@ -6784,7 +6788,7 @@
       <c r="H86" s="5" t="n"/>
       <c r="I86" s="6" t="inlineStr">
         <is>
-          <t>Quelle part de votre chiffre d'affaires vient de ce que vous vendez en plus : {hors_location} ?</t>
+          <t>Sur les 12 derniers mois, quelle part de votre chiffre d'affaires vient de ce que vous vendez en plus : {hors_location} ?</t>
         </is>
       </c>
       <c r="J86" s="7" t="n"/>
@@ -6869,8 +6873,12 @@
           <t>%</t>
         </is>
       </c>
-      <c r="N87" s="7" t="n"/>
-      <c r="O87" s="7" t="n"/>
+      <c r="N87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="6" t="n">
+        <v>100</v>
+      </c>
       <c r="P87" s="7" t="n"/>
       <c r="Q87" s="7" t="n"/>
       <c r="R87" s="7" t="n"/>
@@ -7150,7 +7158,7 @@
       <c r="P91" s="7" t="n"/>
       <c r="Q91" s="6" t="inlineStr">
         <is>
-          <t>Nombre [nombre] · Montant estimé [€ 0-]</t>
+          <t>Nombre [nombre 0-] · Montant estimé [€ 0-]</t>
         </is>
       </c>
       <c r="R91" s="7" t="n"/>
@@ -7342,7 +7350,7 @@
       <c r="H94" s="5" t="n"/>
       <c r="I94" s="6" t="inlineStr">
         <is>
-          <t>Quelle part de votre chiffre d'affaires fait chacune de ces offres ?</t>
+          <t>Sur les 12 derniers mois, quelle part de votre chiffre d'affaires a fait chacune de ces offres ?</t>
         </is>
       </c>
       <c r="J94" s="6" t="inlineStr">
@@ -9228,12 +9236,12 @@
       <c r="H121" s="5" t="n"/>
       <c r="I121" s="6" t="inlineStr">
         <is>
-          <t>Parmi vos clients de l'an dernier, quelle part vous a de nouveau choisi cette année ?</t>
+          <t>Parmi vos clients de l'année d'avant, quelle part vous a de nouveau choisi sur les 12 derniers mois ?</t>
         </is>
       </c>
       <c r="J121" s="6" t="inlineStr">
         <is>
-          <t>Une estimation suffit. Si vous ne connaissez pas vos clients par leur nom, estimez la part d'habitués.</t>
+          <t>L'année d'avant : les 12 mois qui précèdent les 12 derniers mois. Une estimation suffit. Si vous ne connaissez pas vos clients par leur nom, estimez la part d'habitués.</t>
         </is>
       </c>
       <c r="K121" s="7" t="n"/>
@@ -9722,7 +9730,7 @@
       <c r="P128" s="7" t="n"/>
       <c r="Q128" s="6" t="inlineStr">
         <is>
-          <t>Clients sous contrat ou abonnés [nombre] · Total payé par mois [€ 0-]</t>
+          <t>Clients sous contrat ou abonnés [nombre 0-] · Total payé par mois [€ 0-]</t>
         </is>
       </c>
       <c r="R128" s="7" t="n"/>
@@ -9788,7 +9796,7 @@
       <c r="P129" s="7" t="n"/>
       <c r="Q129" s="6" t="inlineStr">
         <is>
-          <t>Clients sous contrat ou abonnés [nombre] · Total payé par mois [€ 0-]</t>
+          <t>Clients sous contrat ou abonnés [nombre 0-] · Total payé par mois [€ 0-]</t>
         </is>
       </c>
       <c r="R129" s="6" t="inlineStr">
@@ -10227,7 +10235,11 @@
           <t>À quel moment demandez-vous à vos clients de vous recommander ?</t>
         </is>
       </c>
-      <c r="J136" s="7" t="n"/>
+      <c r="J136" s="6" t="inlineStr">
+        <is>
+          <t>Si vous le faites à plusieurs moments, choisissez le plus fréquent.</t>
+        </is>
+      </c>
       <c r="K136" s="7" t="n"/>
       <c r="L136" s="6" t="inlineStr">
         <is>
@@ -11138,7 +11150,7 @@
       <c r="P149" s="7" t="n"/>
       <c r="Q149" s="6" t="inlineStr">
         <is>
-          <t>Personnes [nombre] · Dont à temps partiel [nombre]</t>
+          <t>Personnes [nombre 0-] · Dont à temps partiel [nombre 0-]</t>
         </is>
       </c>
       <c r="R149" s="6" t="inlineStr">
@@ -11352,7 +11364,7 @@
       <c r="P152" s="7" t="n"/>
       <c r="Q152" s="6" t="inlineStr">
         <is>
-          <t>Heures travaillées [heures] · Heures facturées [heures]</t>
+          <t>Heures travaillées [heures 0-] · Heures facturées [heures 0-]</t>
         </is>
       </c>
       <c r="R152" s="7" t="n"/>
@@ -11554,7 +11566,7 @@
       <c r="P155" s="7" t="n"/>
       <c r="Q155" s="6" t="inlineStr">
         <is>
-          <t>Heures d'ouverture [heures]</t>
+          <t>Heures d'ouverture [heures 0-]</t>
         </is>
       </c>
       <c r="R155" s="6" t="inlineStr">
@@ -11986,7 +11998,7 @@
       <c r="P161" s="7" t="n"/>
       <c r="Q161" s="6" t="inlineStr">
         <is>
-          <t>Clients perdus par mois [nombre]</t>
+          <t>Clients perdus par mois [nombre 0-]</t>
         </is>
       </c>
       <c r="R161" s="6" t="inlineStr">
@@ -12266,7 +12278,7 @@
       <c r="P165" s="7" t="n"/>
       <c r="Q165" s="6" t="inlineStr">
         <is>
-          <t>Nombre [nombre]</t>
+          <t>Nombre [nombre 0-]</t>
         </is>
       </c>
       <c r="R165" s="6" t="inlineStr">
@@ -12340,7 +12352,7 @@
       <c r="P166" s="7" t="n"/>
       <c r="Q166" s="6" t="inlineStr">
         <is>
-          <t>Heures par semaine [heures] · Budget par mois [€ 0-]</t>
+          <t>Heures par semaine [heures 0-] · Budget par mois [€ 0-]</t>
         </is>
       </c>
       <c r="R166" s="7" t="n"/>
@@ -12410,7 +12422,7 @@
       <c r="P167" s="7" t="n"/>
       <c r="Q167" s="6" t="inlineStr">
         <is>
-          <t>Courses [nombre] · Heures disponibles [heures] · Heures avec un client ou un colis [heures]</t>
+          <t>Courses [nombre 0-] · Heures disponibles [heures 0-] · Heures avec un client ou un colis [heures 0-]</t>
         </is>
       </c>
       <c r="R167" s="7" t="n"/>
@@ -12480,7 +12492,7 @@
       <c r="P168" s="7" t="n"/>
       <c r="Q168" s="6" t="inlineStr">
         <is>
-          <t>Kilomètres au total [km] · Dont avec un client ou un colis [km]</t>
+          <t>Kilomètres au total [km 0-] · Dont avec un client ou un colis [km 0-]</t>
         </is>
       </c>
       <c r="R168" s="7" t="n"/>
@@ -12545,7 +12557,9 @@
           <t>nombre</t>
         </is>
       </c>
-      <c r="N169" s="7" t="n"/>
+      <c r="N169" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="O169" s="7" t="n"/>
       <c r="P169" s="7" t="n"/>
       <c r="Q169" s="7" t="n"/>
@@ -12611,8 +12625,12 @@
           <t>%</t>
         </is>
       </c>
-      <c r="N170" s="7" t="n"/>
-      <c r="O170" s="7" t="n"/>
+      <c r="N170" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" s="6" t="n">
+        <v>100</v>
+      </c>
       <c r="P170" s="7" t="n"/>
       <c r="Q170" s="7" t="n"/>
       <c r="R170" s="7" t="n"/>
@@ -12673,8 +12691,12 @@
           <t>%</t>
         </is>
       </c>
-      <c r="N171" s="7" t="n"/>
-      <c r="O171" s="7" t="n"/>
+      <c r="N171" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" s="6" t="n">
+        <v>100</v>
+      </c>
       <c r="P171" s="7" t="n"/>
       <c r="Q171" s="7" t="n"/>
       <c r="R171" s="7" t="n"/>
@@ -12880,7 +12902,7 @@
       <c r="P174" s="7" t="n"/>
       <c r="Q174" s="6" t="inlineStr">
         <is>
-          <t>Votre délai [jours] · Délai des concurrents [jours]</t>
+          <t>Votre délai [jours 0-] · Délai des concurrents [jours 0-]</t>
         </is>
       </c>
       <c r="R174" s="7" t="n"/>
@@ -12950,7 +12972,7 @@
       <c r="P175" s="7" t="n"/>
       <c r="Q175" s="6" t="inlineStr">
         <is>
-          <t>Biens en stock [nombre] · Jours en stock en moyenne [jours]</t>
+          <t>Biens en stock [nombre 0-] · Jours en stock en moyenne [jours 0-]</t>
         </is>
       </c>
       <c r="R175" s="7" t="n"/>
@@ -13019,8 +13041,12 @@
           <t>%</t>
         </is>
       </c>
-      <c r="N176" s="7" t="n"/>
-      <c r="O176" s="7" t="n"/>
+      <c r="N176" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O176" s="6" t="n">
+        <v>100</v>
+      </c>
       <c r="P176" s="7" t="n"/>
       <c r="Q176" s="7" t="n"/>
       <c r="R176" s="7" t="n"/>
@@ -13151,7 +13177,9 @@
           <t>nombre</t>
         </is>
       </c>
-      <c r="N178" s="7" t="n"/>
+      <c r="N178" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="O178" s="7" t="n"/>
       <c r="P178" s="7" t="n"/>
       <c r="Q178" s="7" t="n"/>
@@ -13214,7 +13242,7 @@
       <c r="P179" s="7" t="n"/>
       <c r="Q179" s="6" t="inlineStr">
         <is>
-          <t>Mandats [nombre] · Dont exclusifs [nombre]</t>
+          <t>Mandats [nombre 0-] · Dont exclusifs [nombre 0-]</t>
         </is>
       </c>
       <c r="R179" s="7" t="n"/>
@@ -13279,7 +13307,9 @@
           <t>jours</t>
         </is>
       </c>
-      <c r="N180" s="7" t="n"/>
+      <c r="N180" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="O180" s="7" t="n"/>
       <c r="P180" s="7" t="n"/>
       <c r="Q180" s="7" t="n"/>
@@ -13345,8 +13375,12 @@
           <t>%</t>
         </is>
       </c>
-      <c r="N181" s="7" t="n"/>
-      <c r="O181" s="7" t="n"/>
+      <c r="N181" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" s="6" t="n">
+        <v>100</v>
+      </c>
       <c r="P181" s="7" t="n"/>
       <c r="Q181" s="7" t="n"/>
       <c r="R181" s="7" t="n"/>
@@ -13407,7 +13441,9 @@
           <t>nombre</t>
         </is>
       </c>
-      <c r="N182" s="7" t="n"/>
+      <c r="N182" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="O182" s="7" t="n"/>
       <c r="P182" s="7" t="n"/>
       <c r="Q182" s="7" t="n"/>
@@ -13602,7 +13638,7 @@
       <c r="H185" s="5" t="n"/>
       <c r="I185" s="6" t="inlineStr">
         <is>
-          <t>Quelle part de votre chiffre d'affaires fait chacune de ces offres ?</t>
+          <t>Sur les 12 derniers mois, quelle part de votre chiffre d'affaires a fait chacune de ces offres ?</t>
         </is>
       </c>
       <c r="J185" s="6" t="inlineStr">
@@ -13774,7 +13810,7 @@
       <c r="P187" s="7" t="n"/>
       <c r="Q187" s="6" t="inlineStr">
         <is>
-          <t>Heures par mois [heures]</t>
+          <t>Heures par mois [heures 0-]</t>
         </is>
       </c>
       <c r="R187" s="6" t="inlineStr">
@@ -14404,7 +14440,7 @@
       <c r="P196" s="7" t="n"/>
       <c r="Q196" s="6" t="inlineStr">
         <is>
-          <t>Clients sous contrat ou abonnés [nombre] · Total payé par mois [€ 0-]</t>
+          <t>Clients sous contrat ou abonnés [nombre 0-] · Total payé par mois [€ 0-]</t>
         </is>
       </c>
       <c r="R196" s="7" t="n"/>
@@ -14894,7 +14930,7 @@
       <c r="P203" s="7" t="n"/>
       <c r="Q203" s="6" t="inlineStr">
         <is>
-          <t>Heures travaillées [heures] · Heures facturées [heures]</t>
+          <t>Heures travaillées [heures 0-] · Heures facturées [heures 0-]</t>
         </is>
       </c>
       <c r="R203" s="7" t="n"/>
@@ -15034,7 +15070,7 @@
       <c r="P205" s="7" t="n"/>
       <c r="Q205" s="6" t="inlineStr">
         <is>
-          <t>Heures [heures] · Coût [€ 0-]</t>
+          <t>Heures [heures 0-] · Coût [€ 0-]</t>
         </is>
       </c>
       <c r="R205" s="7" t="n"/>
@@ -15592,7 +15628,7 @@
       <c r="P213" s="7" t="n"/>
       <c r="Q213" s="6" t="inlineStr">
         <is>
-          <t>Coût par mois [€ 0-] · Utilisateurs [nombre] · Renouvellement [mois et année] · Résiliation [choix: À tout moment / Durée minimum à respecter] · Utilisation [choix: Utilisé / Peu utilisé / Pas utilisé]</t>
+          <t>Coût par mois [€ 0-] · Utilisateurs [nombre 0-] · Renouvellement [mois et année] · Résiliation [choix: À tout moment / Durée minimum à respecter] · Utilisation [choix: Utilisé / Peu utilisé / Pas utilisé]</t>
         </is>
       </c>
       <c r="R213" s="6" t="inlineStr">
@@ -15866,7 +15902,7 @@
       <c r="P217" s="7" t="n"/>
       <c r="Q217" s="6" t="inlineStr">
         <is>
-          <t>Reprises par mois [nombre] · Retours par mois [nombre] · Gestes commerciaux par mois [nombre] · Coût moyen d'une reprise [€ 0-] · Coût moyen d'un geste commercial [€ 0-]</t>
+          <t>Reprises par mois [nombre 0-] · Retours par mois [nombre 0-] · Gestes commerciaux par mois [nombre 0-] · Coût moyen d'une reprise [€ 0-] · Coût moyen d'un geste commercial [€ 0-]</t>
         </is>
       </c>
       <c r="R217" s="7" t="n"/>
@@ -16776,7 +16812,7 @@
       <c r="P230" s="7" t="n"/>
       <c r="Q230" s="6" t="inlineStr">
         <is>
-          <t>Montant [€ 0-] · Mois pour vous en remettre [mois]</t>
+          <t>Montant [€ 0-] · Mois pour vous en remettre [mois 0-]</t>
         </is>
       </c>
       <c r="R230" s="7" t="n"/>
@@ -17066,7 +17102,7 @@
       <c r="P234" s="7" t="n"/>
       <c r="Q234" s="6" t="inlineStr">
         <is>
-          <t>Nombre [nombre] · Montant [€ 0-]</t>
+          <t>Nombre [nombre 0-] · Montant [€ 0-]</t>
         </is>
       </c>
       <c r="R234" s="7" t="n"/>
@@ -17192,7 +17228,7 @@
       </c>
       <c r="I236" s="6" t="inlineStr">
         <is>
-          <t>En réalité, en combien de temps vos clients vous paient-ils ?</t>
+          <t>Sur les 12 derniers mois, en combien de temps vos clients vous ont-ils payé en réalité ?</t>
         </is>
       </c>
       <c r="J236" s="6" t="inlineStr">
@@ -17290,7 +17326,7 @@
       <c r="P237" s="7" t="n"/>
       <c r="Q237" s="6" t="inlineStr">
         <is>
-          <t>Délai réel de paiement [jours]</t>
+          <t>Délai réel de paiement [jours 0-]</t>
         </is>
       </c>
       <c r="R237" s="6" t="inlineStr">
@@ -17722,7 +17758,7 @@
       <c r="P243" s="7" t="n"/>
       <c r="Q243" s="6" t="inlineStr">
         <is>
-          <t>Jours avant la première relance [jours] · Méthode [choix: Toujours, par écrit / Au cas par cas / Aucune relance]</t>
+          <t>Jours avant la première relance [jours 0-] · Méthode [choix: Toujours, par écrit / Au cas par cas / Aucune relance]</t>
         </is>
       </c>
       <c r="R243" s="7" t="n"/>
@@ -17792,7 +17828,7 @@
       <c r="P244" s="7" t="n"/>
       <c r="Q244" s="6" t="inlineStr">
         <is>
-          <t>Nombre de factures [nombre] · Montant [€ 0-]</t>
+          <t>Nombre de factures [nombre 0-] · Montant [€ 0-]</t>
         </is>
       </c>
       <c r="R244" s="7" t="n"/>
@@ -19076,7 +19112,7 @@
       <c r="P262" s="7" t="n"/>
       <c r="Q262" s="6" t="inlineStr">
         <is>
-          <t>Objet [texte] · Prix d'achat [€ 0-] · Installation et frais annexes [€ 0-] · Coûts récurrents par mois [€ 0-] · Mise en service [mois et année] · Durée d'utilisation prévue [ans]</t>
+          <t>Objet [texte] · Prix d'achat [€ 0-] · Installation et frais annexes [€ 0-] · Coûts récurrents par mois [€ 0-] · Mise en service [mois et année] · Durée d'utilisation prévue [ans 0-]</t>
         </is>
       </c>
       <c r="R262" s="7" t="n"/>
@@ -19222,7 +19258,7 @@
       <c r="P264" s="7" t="n"/>
       <c r="Q264" s="6" t="inlineStr">
         <is>
-          <t>Chiffre d'affaires en plus [€ 0-] · Économies de charges [€ 0-] · Heures gagnées [heures]</t>
+          <t>Chiffre d'affaires en plus [€ 0-] · Économies de charges [€ 0-] · Heures gagnées [heures 0-]</t>
         </is>
       </c>
       <c r="R264" s="7" t="n"/>
@@ -19296,7 +19332,7 @@
       <c r="P265" s="7" t="n"/>
       <c r="Q265" s="6" t="inlineStr">
         <is>
-          <t>Chiffre d'affaires en plus [€ 0-] · Économies de charges [€ 0-] · Heures gagnées [heures]</t>
+          <t>Chiffre d'affaires en plus [€ 0-] · Économies de charges [€ 0-] · Heures gagnées [heures 0-]</t>
         </is>
       </c>
       <c r="R265" s="7" t="n"/>
@@ -19772,7 +19808,7 @@
       <c r="P272" s="7" t="n"/>
       <c r="Q272" s="6" t="inlineStr">
         <is>
-          <t>Heures par mois [heures] · Qui [choix: Vous / Un salarié / Le comptable / Un prestataire]</t>
+          <t>Heures par mois [heures 0-] · Qui [choix: Vous / Un salarié / Le comptable / Un prestataire]</t>
         </is>
       </c>
       <c r="R272" s="7" t="n"/>
@@ -20634,7 +20670,7 @@
       <c r="P284" s="7" t="n"/>
       <c r="Q284" s="6" t="inlineStr">
         <is>
-          <t>Ruptures par mois [nombre] · Durée moyenne [jours]</t>
+          <t>Ruptures par mois [nombre 0-] · Durée moyenne [jours 0-]</t>
         </is>
       </c>
       <c r="R284" s="7" t="n"/>
@@ -20708,7 +20744,7 @@
       <c r="P285" s="7" t="n"/>
       <c r="Q285" s="6" t="inlineStr">
         <is>
-          <t>Clients perdus par mois [nombre] · Commandes reportées par mois [nombre]</t>
+          <t>Clients perdus par mois [nombre 0-] · Commandes reportées par mois [nombre 0-]</t>
         </is>
       </c>
       <c r="R285" s="7" t="n"/>
@@ -20778,7 +20814,7 @@
       <c r="P286" s="7" t="n"/>
       <c r="Q286" s="6" t="inlineStr">
         <is>
-          <t>Commandes par mois [nombre] · Méthode [choix: Un seuil de commande pour chaque produit / Un seuil pour les principaux produits / À l'instinct]</t>
+          <t>Commandes par mois [nombre 0-] · Méthode [choix: Un seuil de commande pour chaque produit / Un seuil pour les principaux produits / À l'instinct]</t>
         </is>
       </c>
       <c r="R286" s="7" t="n"/>
@@ -20920,7 +20956,7 @@
       <c r="P288" s="7" t="n"/>
       <c r="Q288" s="6" t="inlineStr">
         <is>
-          <t>Fournisseurs avec un minimum [nombre] · Part du stock achetée seulement pour atteindre ce minimum [% 0-100] · Remise obtenue grâce au volume [% 0-100]</t>
+          <t>Fournisseurs avec un minimum [nombre 0-] · Part du stock achetée seulement pour atteindre ce minimum [% 0-100] · Remise obtenue grâce au volume [% 0-100]</t>
         </is>
       </c>
       <c r="R288" s="7" t="n"/>
@@ -20990,7 +21026,7 @@
       <c r="P289" s="7" t="n"/>
       <c r="Q289" s="6" t="inlineStr">
         <is>
-          <t>Inventaires par an [nombre] · Dernier inventaire [mois et année] · Outil [choix: Aucun / Tableur / Logiciel relié à la caisse]</t>
+          <t>Inventaires par an [nombre 0-] · Dernier inventaire [mois et année] · Outil [choix: Aucun / Tableur / Logiciel relié à la caisse]</t>
         </is>
       </c>
       <c r="R289" s="7" t="n"/>
@@ -21134,7 +21170,7 @@
       <c r="P291" s="7" t="n"/>
       <c r="Q291" s="6" t="inlineStr">
         <is>
-          <t>Écart à l'inventaire précédent [€ 0-] · Corrections à la main par mois (moyenne des 3 derniers mois) [nombre]</t>
+          <t>Écart à l'inventaire précédent [€ 0-] · Corrections à la main par mois (moyenne des 3 derniers mois) [nombre 0-]</t>
         </is>
       </c>
       <c r="R291" s="7" t="n"/>
@@ -21806,7 +21842,7 @@
       <c r="P301" s="7" t="n"/>
       <c r="Q301" s="6" t="inlineStr">
         <is>
-          <t>Heures par mois [heures]</t>
+          <t>Heures par mois [heures 0-]</t>
         </is>
       </c>
       <c r="R301" s="6" t="inlineStr">
@@ -22558,7 +22594,7 @@
       <c r="P312" s="7" t="n"/>
       <c r="Q312" s="6" t="inlineStr">
         <is>
-          <t>Jours [jours] · Heures [heures]</t>
+          <t>Jours [jours 0-] · Heures [heures 0-]</t>
         </is>
       </c>
       <c r="R312" s="7" t="n"/>
@@ -23164,7 +23200,7 @@
       <c r="P321" s="7" t="n"/>
       <c r="Q321" s="6" t="inlineStr">
         <is>
-          <t>Heures [heures] · Coût [€ 0-]</t>
+          <t>Heures [heures 0-] · Coût [€ 0-]</t>
         </is>
       </c>
       <c r="R321" s="7" t="n"/>
@@ -23504,7 +23540,7 @@
       <c r="P326" s="7" t="n"/>
       <c r="Q326" s="6" t="inlineStr">
         <is>
-          <t>Heures en plus par semaine [heures]</t>
+          <t>Heures en plus par semaine [heures 0-]</t>
         </is>
       </c>
       <c r="R326" s="6" t="inlineStr">
@@ -24759,7 +24795,7 @@
       <c r="O345" s="7" t="n"/>
       <c r="P345" s="6" t="inlineStr">
         <is>
-          <t>Intérim ou extras · Heures supplémentaires · Rien de particulier</t>
+          <t>Intérim ou extras · Heures supplémentaires · Rien de particulier · Les deux</t>
         </is>
       </c>
       <c r="Q345" s="7" t="n"/>
@@ -24830,7 +24866,7 @@
       <c r="P346" s="7" t="n"/>
       <c r="Q346" s="6" t="inlineStr">
         <is>
-          <t>Tâches clés [nombre] · Dont décrites par écrit [nombre]</t>
+          <t>Tâches clés [nombre 0-] · Dont décrites par écrit [nombre 0-]</t>
         </is>
       </c>
       <c r="R346" s="7" t="n"/>
@@ -25302,7 +25338,7 @@
       <c r="P353" s="7" t="n"/>
       <c r="Q353" s="6" t="inlineStr">
         <is>
-          <t>Reprises par mois [nombre] · Temps moyen d'une reprise [heures]</t>
+          <t>Reprises par mois [nombre 0-] · Temps moyen d'une reprise [heures 0-]</t>
         </is>
       </c>
       <c r="R353" s="7" t="n"/>
@@ -25442,7 +25478,7 @@
       <c r="P355" s="7" t="n"/>
       <c r="Q355" s="6" t="inlineStr">
         <is>
-          <t>Corrections mineures [nombre] · Reprises complètes [nombre]</t>
+          <t>Corrections mineures [nombre 0-] · Reprises complètes [nombre 0-]</t>
         </is>
       </c>
       <c r="R355" s="7" t="n"/>
@@ -25582,7 +25618,7 @@
       <c r="P357" s="7" t="n"/>
       <c r="Q357" s="6" t="inlineStr">
         <is>
-          <t>Laquelle [texte] · Heures par semaine [heures] · Qui la fait [texte] · Outil utilisé [texte]</t>
+          <t>Laquelle [texte] · Heures par semaine [heures 0-] · Qui la fait [texte] · Outil utilisé [texte]</t>
         </is>
       </c>
       <c r="R357" s="6" t="inlineStr">
@@ -25784,7 +25820,7 @@
       <c r="P360" s="7" t="n"/>
       <c r="Q360" s="6" t="inlineStr">
         <is>
-          <t>Réunions par mois [nombre] · Durée moyenne en minutes [nombre] · Participants en moyenne [nombre]</t>
+          <t>Réunions par mois [nombre 0-] · Durée moyenne en minutes [nombre 0-] · Participants en moyenne [nombre 0-]</t>
         </is>
       </c>
       <c r="R360" s="7" t="n"/>
@@ -26188,7 +26224,7 @@
       <c r="P366" s="7" t="n"/>
       <c r="Q366" s="6" t="inlineStr">
         <is>
-          <t>Moyen prévu [oui / non] · Idées appliquées sur 6 mois [nombre]</t>
+          <t>Moyen prévu [oui / non] · Idées appliquées sur 6 mois [nombre 0-]</t>
         </is>
       </c>
       <c r="R366" s="7" t="n"/>
@@ -26398,7 +26434,7 @@
       <c r="P369" s="7" t="n"/>
       <c r="Q369" s="6" t="inlineStr">
         <is>
-          <t>Jours de formation [jours] · Transmission organisée entre collègues [oui / non]</t>
+          <t>Jours de formation [jours 0-] · Transmission organisée entre collègues [oui / non]</t>
         </is>
       </c>
       <c r="R369" s="7" t="n"/>
@@ -26878,7 +26914,7 @@
       <c r="P376" s="7" t="n"/>
       <c r="Q376" s="6" t="inlineStr">
         <is>
-          <t>Candidatures par poste [nombre] · Entretiens par poste [nombre] · Candidats qui ont refusé l'offre [nombre]</t>
+          <t>Candidatures par poste [nombre 0-] · Entretiens par poste [nombre 0-] · Candidats qui ont refusé l'offre [nombre 0-]</t>
         </is>
       </c>
       <c r="R376" s="7" t="n"/>
@@ -26952,7 +26988,7 @@
       <c r="P377" s="7" t="n"/>
       <c r="Q377" s="6" t="inlineStr">
         <is>
-          <t>Coût d'un recrutement [€ 0-] · Heures passées par vous et votre équipe [heures]</t>
+          <t>Coût d'un recrutement [€ 0-] · Heures passées par vous et votre équipe [heures 0-]</t>
         </is>
       </c>
       <c r="R377" s="7" t="n"/>
@@ -27508,7 +27544,7 @@
       <c r="P385" s="7" t="n"/>
       <c r="Q385" s="6" t="inlineStr">
         <is>
-          <t>Poste [texte] · Semaines pour le maîtriser [semaines]</t>
+          <t>Poste [texte] · Semaines pour le maîtriser [semaines 0-]</t>
         </is>
       </c>
       <c r="R385" s="7" t="n"/>
@@ -27574,7 +27610,7 @@
       <c r="P386" s="7" t="n"/>
       <c r="Q386" s="6" t="inlineStr">
         <is>
-          <t>Départs [nombre]</t>
+          <t>Départs [nombre 0-]</t>
         </is>
       </c>
       <c r="R386" s="6" t="inlineStr">
@@ -27644,7 +27680,7 @@
       <c r="P387" s="7" t="n"/>
       <c r="Q387" s="6" t="inlineStr">
         <is>
-          <t>Départs sur un poste clé [nombre] · Remplacement [choix: Fait / En cours / Non]</t>
+          <t>Départs sur un poste clé [nombre 0-] · Remplacement [choix: Fait / En cours / Non]</t>
         </is>
       </c>
       <c r="R387" s="7" t="n"/>
@@ -27784,7 +27820,7 @@
       <c r="P389" s="7" t="n"/>
       <c r="Q389" s="6" t="inlineStr">
         <is>
-          <t>Poste le plus concerné [texte] · Ancienneté moyenne au départ [mois]</t>
+          <t>Poste le plus concerné [texte] · Ancienneté moyenne au départ [mois 0-]</t>
         </is>
       </c>
       <c r="R389" s="7" t="n"/>
@@ -27920,7 +27956,7 @@
       <c r="P391" s="7" t="n"/>
       <c r="Q391" s="6" t="inlineStr">
         <is>
-          <t>À l'initiative de la recrue [nombre] · À votre initiative [nombre]</t>
+          <t>À l'initiative de la recrue [nombre 0-] · À votre initiative [nombre 0-]</t>
         </is>
       </c>
       <c r="R391" s="6" t="inlineStr">
@@ -28404,7 +28440,7 @@
       <c r="P398" s="7" t="n"/>
       <c r="Q398" s="6" t="inlineStr">
         <is>
-          <t>Semaines pour former un remplaçant [semaines]</t>
+          <t>Semaines pour former un remplaçant [semaines 0-]</t>
         </is>
       </c>
       <c r="R398" s="6" t="inlineStr">
@@ -28621,7 +28657,7 @@
       <c r="O401" s="7" t="n"/>
       <c r="P401" s="6" t="inlineStr">
         <is>
-          <t>Préparés avec l'équipe · Annoncés · Imposés</t>
+          <t>Préparés avec l'équipe · Annoncés · Imposés · Aucun changement récent</t>
         </is>
       </c>
       <c r="Q401" s="7" t="n"/>
@@ -28972,7 +29008,7 @@
       <c r="P406" s="7" t="n"/>
       <c r="Q406" s="6" t="inlineStr">
         <is>
-          <t>Heures par semaine [heures] · S'apprend en moins d'un mois [oui / non] · Méthode écrite [oui / non]</t>
+          <t>Heures par semaine [heures 0-] · S'apprend en moins d'un mois [oui / non] · Méthode écrite [oui / non]</t>
         </is>
       </c>
       <c r="R406" s="6" t="inlineStr">
@@ -29186,7 +29222,7 @@
       <c r="P409" s="7" t="n"/>
       <c r="Q409" s="6" t="inlineStr">
         <is>
-          <t>Clients perdus par mois [nombre]</t>
+          <t>Clients perdus par mois [nombre 0-]</t>
         </is>
       </c>
       <c r="R409" s="6" t="inlineStr">
@@ -29748,7 +29784,7 @@
       <c r="P417" s="7" t="n"/>
       <c r="Q417" s="6" t="inlineStr">
         <is>
-          <t>Personnes [nombre] · Dont à temps partiel [nombre]</t>
+          <t>Personnes [nombre 0-] · Dont à temps partiel [nombre 0-]</t>
         </is>
       </c>
       <c r="R417" s="6" t="inlineStr">
@@ -29822,7 +29858,7 @@
       <c r="P418" s="7" t="n"/>
       <c r="Q418" s="6" t="inlineStr">
         <is>
-          <t>Personnes [nombre]</t>
+          <t>Personnes [nombre 0-]</t>
         </is>
       </c>
       <c r="R418" s="6" t="inlineStr">
@@ -29892,7 +29928,7 @@
       <c r="P419" s="7" t="n"/>
       <c r="Q419" s="6" t="inlineStr">
         <is>
-          <t>Qui le fait [choix: Vous / Un responsable / Chacun s'organise / Il n'y a pas de planning] · Heures par semaine [heures]</t>
+          <t>Qui le fait [choix: Vous / Un responsable / Chacun s'organise / Il n'y a pas de planning] · Heures par semaine [heures 0-]</t>
         </is>
       </c>
       <c r="R419" s="7" t="n"/>
@@ -30230,7 +30266,7 @@
       <c r="P424" s="7" t="n"/>
       <c r="Q424" s="6" t="inlineStr">
         <is>
-          <t>Responsables, vous non compris [nombre] · Personnes suivies par un responsable, au plus [nombre]</t>
+          <t>Responsables, vous non compris [nombre 0-] · Personnes suivies par un responsable, au plus [nombre 0-]</t>
         </is>
       </c>
       <c r="R424" s="7" t="n"/>
@@ -30419,7 +30455,7 @@
       </c>
       <c r="J427" s="6" t="inlineStr">
         <is>
-          <t>Cochez une catégorie, deux au plus.</t>
+          <t>Répondez « Oui » pour une catégorie, deux au plus.</t>
         </is>
       </c>
       <c r="K427" s="7" t="n"/>
@@ -30914,7 +30950,7 @@
       <c r="P434" s="7" t="n"/>
       <c r="Q434" s="6" t="inlineStr">
         <is>
-          <t>Disponibles [nombre] · Publiées sur le site [nombre] · Publiées sur les réseaux [nombre]</t>
+          <t>Disponibles [nombre 0-] · Publiées sur le site [nombre 0-] · Publiées sur les réseaux [nombre 0-]</t>
         </is>
       </c>
       <c r="R434" s="6" t="inlineStr">
@@ -31186,7 +31222,7 @@
       <c r="P438" s="7" t="n"/>
       <c r="Q438" s="6" t="inlineStr">
         <is>
-          <t>Ouverture du compte [mois et année] · Publications par mois (moyenne des 3 derniers mois) [nombre] · Format principal [choix: Vidéo courte / Vidéo longue / Carrousel / Photo / Texte / Story] · Dernière publication [mois et année] · Qui publie [choix: Vous / Un salarié / Un prestataire]</t>
+          <t>Ouverture du compte [mois et année] · Publications par mois (moyenne des 3 derniers mois) [nombre 0-] · Format principal [choix: Vidéo courte / Vidéo longue / Carrousel / Photo / Texte / Story] · Dernière publication [mois et année] · Qui publie [choix: Vous / Un salarié / Un prestataire]</t>
         </is>
       </c>
       <c r="R438" s="6" t="inlineStr">
@@ -31590,12 +31626,12 @@
       <c r="H444" s="5" t="n"/>
       <c r="I444" s="6" t="inlineStr">
         <is>
-          <t>Quelle part de vos demandes, de vos nouveaux clients et de votre chiffre d'affaires vient de chaque canal ?</t>
+          <t>Sur les 12 derniers mois, quelle part de vos demandes, de vos nouveaux clients et de votre chiffre d'affaires est arrivée par chaque canal ?</t>
         </is>
       </c>
       <c r="J444" s="6" t="inlineStr">
         <is>
-          <t>Une ligne par canal coché. Si l'agent Acquisition a déjà posé ces questions, les réponses sont reprises.</t>
+          <t>Une ligne par canal coché. Chaque colonne fait 100 % : une demande, un client ou un euro ne compte que dans un canal, celui par lequel il est arrivé. Si l'agent Acquisition a déjà posé ces questions, les réponses sont reprises.</t>
         </is>
       </c>
       <c r="K444" s="7" t="n"/>
@@ -31620,7 +31656,7 @@
       </c>
       <c r="S444" s="6" t="inlineStr">
         <is>
-          <t>Part des demandes = 100</t>
+          <t>Part des demandes ; Part des nouveaux clients ; Part du chiffre d'affaires sur 12 mois = 100</t>
         </is>
       </c>
       <c r="T444" s="5" t="inlineStr">
@@ -31834,7 +31870,7 @@
       <c r="P447" s="7" t="n"/>
       <c r="Q447" s="6" t="inlineStr">
         <is>
-          <t>Par mois [nombre]</t>
+          <t>Par mois [nombre 0-]</t>
         </is>
       </c>
       <c r="R447" s="6" t="inlineStr">
@@ -31892,7 +31928,7 @@
       </c>
       <c r="I448" s="6" t="inlineStr">
         <is>
-          <t>D'où viennent les visites de votre site ?</t>
+          <t>Sur les 3 derniers mois, d'où sont venues les visites de votre site ?</t>
         </is>
       </c>
       <c r="J448" s="6" t="inlineStr">
@@ -32338,7 +32374,7 @@
       <c r="P454" s="7" t="n"/>
       <c r="Q454" s="6" t="inlineStr">
         <is>
-          <t>Vues de votre fiche [nombre] · Appels [nombre] · Demandes d'itinéraire [nombre] · Clics vers votre site [nombre]</t>
+          <t>Vues de votre fiche [nombre 0-] · Appels [nombre 0-] · Demandes d'itinéraire [nombre 0-] · Clics vers votre site [nombre 0-]</t>
         </is>
       </c>
       <c r="R454" s="7" t="n"/>
@@ -32412,7 +32448,7 @@
       <c r="P455" s="7" t="n"/>
       <c r="Q455" s="6" t="inlineStr">
         <is>
-          <t>Contacts [nombre]</t>
+          <t>Contacts [nombre 0-]</t>
         </is>
       </c>
       <c r="R455" s="6" t="inlineStr">
@@ -32486,7 +32522,7 @@
       <c r="P456" s="7" t="n"/>
       <c r="Q456" s="6" t="inlineStr">
         <is>
-          <t>Nouveaux contacts par mois [nombre] · Source principale [choix: Site / Offre gratuite / Boutique ou comptoir / Salon ou événement / Réseaux sociaux / Nouveaux clients]</t>
+          <t>Nouveaux contacts par mois [nombre 0-] · Source principale [choix: Site / Offre gratuite / Boutique ou comptoir / Salon ou événement / Réseaux sociaux / Nouveaux clients]</t>
         </is>
       </c>
       <c r="R456" s="7" t="n"/>
@@ -32560,7 +32596,7 @@
       <c r="P457" s="7" t="n"/>
       <c r="Q457" s="6" t="inlineStr">
         <is>
-          <t>Dernier envoi [mois et année] · Envois sur 6 mois [nombre]</t>
+          <t>Dernier envoi [mois et année] · Envois sur 6 mois [nombre 0-]</t>
         </is>
       </c>
       <c r="R457" s="7" t="n"/>
@@ -32630,7 +32666,7 @@
       <c r="P458" s="7" t="n"/>
       <c r="Q458" s="6" t="inlineStr">
         <is>
-          <t>Demandes [nombre] · Clients obtenus [nombre]</t>
+          <t>Demandes [nombre 0-] · Clients obtenus [nombre 0-]</t>
         </is>
       </c>
       <c r="R458" s="7" t="n"/>
@@ -32770,7 +32806,7 @@
       <c r="P460" s="7" t="n"/>
       <c r="Q460" s="6" t="inlineStr">
         <is>
-          <t>Taux d'ouverture [% 0-100] · Taux de clic [% 0-100] · Désinscriptions [nombre] · Réponses [nombre]</t>
+          <t>Taux d'ouverture [% 0-100] · Taux de clic [% 0-100] · Désinscriptions [nombre 0-] · Réponses [nombre 0-]</t>
         </is>
       </c>
       <c r="R460" s="7" t="n"/>
@@ -32980,7 +33016,7 @@
       <c r="P463" s="7" t="n"/>
       <c r="Q463" s="6" t="inlineStr">
         <is>
-          <t>Abonnés [nombre] · Personnes touchées par mois (moyenne des 3 derniers mois) [nombre]</t>
+          <t>Abonnés [nombre 0-] · Personnes touchées par mois (moyenne des 3 derniers mois) [nombre 0-]</t>
         </is>
       </c>
       <c r="R463" s="6" t="inlineStr">
@@ -33054,7 +33090,7 @@
       <c r="P464" s="7" t="n"/>
       <c r="Q464" s="6" t="inlineStr">
         <is>
-          <t>Nouveaux abonnés [nombre] · Désabonnements [nombre]</t>
+          <t>Nouveaux abonnés [nombre 0-] · Désabonnements [nombre 0-]</t>
         </is>
       </c>
       <c r="R464" s="6" t="inlineStr">
@@ -33112,7 +33148,7 @@
       </c>
       <c r="I465" s="6" t="inlineStr">
         <is>
-          <t>Sur chaque réseau, quelle part des personnes touchées ne vous suit pas encore ?</t>
+          <t>Sur les 3 derniers mois, quelle part des personnes touchées sur chaque réseau ne vous suivait pas encore ?</t>
         </is>
       </c>
       <c r="J465" s="6" t="inlineStr">
@@ -33210,7 +33246,7 @@
       <c r="P466" s="7" t="n"/>
       <c r="Q466" s="6" t="inlineStr">
         <is>
-          <t>J'aime [nombre] · Commentaires [nombre] · Partages [nombre] · Enregistrements [nombre]</t>
+          <t>J'aime [nombre 0-] · Commentaires [nombre 0-] · Partages [nombre 0-] · Enregistrements [nombre 0-]</t>
         </is>
       </c>
       <c r="R466" s="6" t="inlineStr">
@@ -33288,7 +33324,7 @@
       <c r="P467" s="7" t="n"/>
       <c r="Q467" s="6" t="inlineStr">
         <is>
-          <t>Clics par mois [nombre] · Destination principale [choix: Site / Fiche Google / Formulaire / Prise de rendez-vous / Téléphone / WhatsApp / Email / Page produit ou offre]</t>
+          <t>Clics par mois [nombre 0-] · Destination principale [choix: Site / Fiche Google / Formulaire / Prise de rendez-vous / Téléphone / WhatsApp / Email / Page produit ou offre]</t>
         </is>
       </c>
       <c r="R467" s="6" t="inlineStr">
@@ -33432,7 +33468,7 @@
       <c r="P469" s="7" t="n"/>
       <c r="Q469" s="6" t="inlineStr">
         <is>
-          <t>Visiteurs de la page de l'offre [nombre] · Contacts récoltés [nombre] · Contacts vraiment intéressés [nombre] · Rendez-vous obtenus [nombre] · Nouveaux clients [nombre]</t>
+          <t>Visiteurs de la page de l'offre [nombre 0-] · Contacts récoltés [nombre 0-] · Contacts vraiment intéressés [nombre 0-] · Rendez-vous obtenus [nombre 0-] · Nouveaux clients [nombre 0-]</t>
         </is>
       </c>
       <c r="R469" s="7" t="n"/>
@@ -33702,12 +33738,12 @@
       </c>
       <c r="I473" s="6" t="inlineStr">
         <is>
-          <t>Parmi les clients et les demandes qui vous viennent des réseaux sociaux, quelle part vient de chaque réseau ?</t>
+          <t>Sur les 12 derniers mois, parmi les demandes qui vous sont venues des réseaux sociaux, quelle part est venue de chaque réseau ?</t>
         </is>
       </c>
       <c r="J473" s="6" t="inlineStr">
         <is>
-          <t>Une estimation suffit. Leur nombre total est déjà demandé avec vos canaux : ici, on le répartit entre vos réseaux.</t>
+          <t>Une estimation suffit. Une demande compte dans un seul réseau : celui par lequel elle est arrivée. Leur nombre total est déjà demandé avec vos canaux : ici, on le répartit entre vos réseaux.</t>
         </is>
       </c>
       <c r="K473" s="7" t="n"/>
@@ -33800,7 +33836,7 @@
       <c r="P474" s="7" t="n"/>
       <c r="Q474" s="6" t="inlineStr">
         <is>
-          <t>Messages par mois [nombre] · Dont demandes commerciales [nombre] · Dont service après-vente [nombre]</t>
+          <t>Messages par mois [nombre 0-] · Dont demandes commerciales [nombre 0-] · Dont service après-vente [nombre 0-]</t>
         </is>
       </c>
       <c r="R474" s="6" t="inlineStr">
@@ -33956,7 +33992,7 @@
       <c r="P476" s="7" t="n"/>
       <c r="Q476" s="6" t="inlineStr">
         <is>
-          <t>Rendez-vous ou devis [nombre] · Nouveaux clients [nombre]</t>
+          <t>Rendez-vous ou devis [nombre 0-] · Nouveaux clients [nombre 0-]</t>
         </is>
       </c>
       <c r="R476" s="7" t="n"/>
@@ -34160,7 +34196,7 @@
       <c r="P479" s="7" t="n"/>
       <c r="Q479" s="6" t="inlineStr">
         <is>
-          <t>Publications [nombre]</t>
+          <t>Publications [nombre 0-]</t>
         </is>
       </c>
       <c r="R479" s="6" t="inlineStr">
@@ -34450,7 +34486,7 @@
       <c r="P483" s="7" t="n"/>
       <c r="Q483" s="6" t="inlineStr">
         <is>
-          <t>Heures par semaine [heures]</t>
+          <t>Heures par semaine [heures 0-]</t>
         </is>
       </c>
       <c r="R483" s="6" t="inlineStr">
@@ -34974,7 +35010,7 @@
       <c r="P490" s="7" t="n"/>
       <c r="Q490" s="6" t="inlineStr">
         <is>
-          <t>Semaines avec une publication [nombre 0-12] · Plus longue pause [semaines]</t>
+          <t>Semaines avec une publication [nombre 0-12] · Plus longue pause [semaines 0-]</t>
         </is>
       </c>
       <c r="R490" s="6" t="inlineStr">
@@ -35194,7 +35230,7 @@
       <c r="P493" s="7" t="n"/>
       <c r="Q493" s="6" t="inlineStr">
         <is>
-          <t>Prêts ou programmés [nombre] · À finaliser [nombre] · Idées notées [nombre]</t>
+          <t>Prêts ou programmés [nombre 0-] · À finaliser [nombre 0-] · Idées notées [nombre 0-]</t>
         </is>
       </c>
       <c r="R493" s="7" t="n"/>
@@ -35264,7 +35300,7 @@
       <c r="P494" s="7" t="n"/>
       <c r="Q494" s="6" t="inlineStr">
         <is>
-          <t>Autres photos et vidéos utilisables : équipe, coulisses, lieu [nombre] · Modèles de visuels [oui / non] · Contenus intemporels à republier [nombre]</t>
+          <t>Autres photos et vidéos utilisables : équipe, coulisses, lieu [nombre 0-] · Modèles de visuels [oui / non] · Contenus intemporels à republier [nombre 0-]</t>
         </is>
       </c>
       <c r="R494" s="7" t="n"/>
@@ -35338,7 +35374,7 @@
       <c r="P495" s="7" t="n"/>
       <c r="Q495" s="6" t="inlineStr">
         <is>
-          <t>Abonnés il y a 6 mois [nombre]</t>
+          <t>Abonnés il y a 6 mois [nombre 0-]</t>
         </is>
       </c>
       <c r="R495" s="6" t="inlineStr">
@@ -35416,7 +35452,7 @@
       <c r="P496" s="7" t="n"/>
       <c r="Q496" s="6" t="inlineStr">
         <is>
-          <t>Réseau [texte] · Personnes touchées [nombre] · Réactions [nombre] · Visites du profil [nombre] · Nouveaux abonnés [nombre] · Clics [nombre] · Messages ou demandes [nombre]</t>
+          <t>Réseau [texte] · Personnes touchées [nombre 0-] · Réactions [nombre 0-] · Visites du profil [nombre 0-] · Nouveaux abonnés [nombre 0-] · Clics [nombre 0-] · Messages ou demandes [nombre 0-]</t>
         </is>
       </c>
       <c r="R496" s="6" t="inlineStr">
@@ -35474,7 +35510,7 @@
       </c>
       <c r="I497" s="6" t="inlineStr">
         <is>
-          <t>Pour chacune de ces 6 publications, quel est son texte et son lien ?</t>
+          <t>Pour vos 3 meilleures et vos 3 moins bonnes publications des 3 derniers mois, quel est leur texte et leur lien ?</t>
         </is>
       </c>
       <c r="J497" s="6" t="inlineStr">
@@ -35568,7 +35604,7 @@
       <c r="P498" s="7" t="n"/>
       <c r="Q498" s="6" t="inlineStr">
         <is>
-          <t>Vues par vidéo [nombre] · Secondes regardées en moyenne [nombre] · Part vue jusqu'au bout [% 0-100]</t>
+          <t>Vues par vidéo [nombre 0-] · Secondes regardées en moyenne [nombre 0-] · Part vue jusqu'au bout [% 0-100]</t>
         </is>
       </c>
       <c r="R498" s="7" t="n"/>
@@ -35968,7 +36004,7 @@
       <c r="P504" s="7" t="n"/>
       <c r="Q504" s="6" t="inlineStr">
         <is>
-          <t>Avis au total [nombre] · Note sur 5 [nombre 0-5] · Avis reçus sur les 6 derniers mois [nombre]</t>
+          <t>Avis au total [nombre 0-] · Note sur 5 [nombre 0-5] · Avis reçus sur les 6 derniers mois [nombre 0-]</t>
         </is>
       </c>
       <c r="R504" s="7" t="n"/>
@@ -36038,7 +36074,7 @@
       <c r="P505" s="7" t="n"/>
       <c r="Q505" s="6" t="inlineStr">
         <is>
-          <t>Avis [nombre] · Note sur 5 [nombre 0-5]</t>
+          <t>Avis [nombre 0-] · Note sur 5 [nombre 0-5]</t>
         </is>
       </c>
       <c r="R505" s="6" t="inlineStr">
@@ -36112,7 +36148,7 @@
       <c r="P506" s="7" t="n"/>
       <c r="Q506" s="6" t="inlineStr">
         <is>
-          <t>5 étoiles [nombre] · 4 étoiles [nombre] · 3 étoiles ou moins [nombre]</t>
+          <t>5 étoiles [nombre 0-] · 4 étoiles [nombre 0-] · 3 étoiles ou moins [nombre 0-]</t>
         </is>
       </c>
       <c r="R506" s="7" t="n"/>
@@ -36388,7 +36424,7 @@
       <c r="P510" s="7" t="n"/>
       <c r="Q510" s="6" t="inlineStr">
         <is>
-          <t>Avis positifs avec une réponse [% 0-100] · Avis négatifs avec une réponse [% 0-100] · Délai moyen de réponse [jours]</t>
+          <t>Avis positifs avec une réponse [% 0-100] · Avis négatifs avec une réponse [% 0-100] · Délai moyen de réponse [jours 0-]</t>
         </is>
       </c>
       <c r="R510" s="7" t="n"/>
@@ -36590,7 +36626,7 @@
       <c r="P513" s="7" t="n"/>
       <c r="Q513" s="6" t="inlineStr">
         <is>
-          <t>Presse [nombre] · Associations ou réseaux locaux [nombre] · Créateurs de contenu [nombre] · Autres entreprises [nombre]</t>
+          <t>Presse [nombre 0-] · Associations ou réseaux locaux [nombre 0-] · Créateurs de contenu [nombre 0-] · Autres entreprises [nombre 0-]</t>
         </is>
       </c>
       <c r="R513" s="7" t="n"/>
@@ -36660,7 +36696,7 @@
       <c r="P514" s="7" t="n"/>
       <c r="Q514" s="6" t="inlineStr">
         <is>
-          <t>Collaborations [nombre] · Ventes suivies [nombre]</t>
+          <t>Collaborations [nombre 0-] · Ventes suivies [nombre 0-]</t>
         </is>
       </c>
       <c r="R514" s="7" t="n"/>
@@ -38308,7 +38344,7 @@
       <c r="P537" s="7" t="n"/>
       <c r="Q537" s="6" t="inlineStr">
         <is>
-          <t>Visites du profil par mois [nombre]</t>
+          <t>Visites du profil par mois [nombre 0-]</t>
         </is>
       </c>
       <c r="R537" s="6" t="inlineStr">
@@ -38608,7 +38644,7 @@
       <c r="P541" s="7" t="n"/>
       <c r="Q541" s="6" t="inlineStr">
         <is>
-          <t>Personnes contactées par mois [nombre] · Devenues clientes par mois [nombre]</t>
+          <t>Personnes contactées par mois [nombre 0-] · Devenues clientes par mois [nombre 0-]</t>
         </is>
       </c>
       <c r="R541" s="7" t="n"/>
@@ -38748,7 +38784,7 @@
       <c r="P543" s="7" t="n"/>
       <c r="Q543" s="6" t="inlineStr">
         <is>
-          <t>Apparitions [nombre] · Clics [nombre] · Position moyenne [nombre 1-100]</t>
+          <t>Apparitions [nombre 0-] · Clics [nombre 0-] · Position moyenne [nombre 1-100]</t>
         </is>
       </c>
       <c r="R543" s="7" t="n"/>
@@ -38822,7 +38858,7 @@
       <c r="P544" s="7" t="n"/>
       <c r="Q544" s="6" t="inlineStr">
         <is>
-          <t>Clics [nombre] · Position moyenne [nombre 1-100]</t>
+          <t>Clics [nombre 0-] · Position moyenne [nombre 1-100]</t>
         </is>
       </c>
       <c r="R544" s="6" t="inlineStr">
@@ -39055,7 +39091,9 @@
           <t>nombre</t>
         </is>
       </c>
-      <c r="N547" s="7" t="n"/>
+      <c r="N547" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="O547" s="7" t="n"/>
       <c r="P547" s="7" t="n"/>
       <c r="Q547" s="7" t="n"/>
@@ -39331,7 +39369,9 @@
           <t>€</t>
         </is>
       </c>
-      <c r="N551" s="7" t="n"/>
+      <c r="N551" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="O551" s="7" t="n"/>
       <c r="P551" s="7" t="n"/>
       <c r="Q551" s="7" t="n"/>
@@ -39402,7 +39442,7 @@
       <c r="P552" s="7" t="n"/>
       <c r="Q552" s="6" t="inlineStr">
         <is>
-          <t>Clics par mois [nombre] · Demandes par mois [nombre]</t>
+          <t>Clics par mois [nombre 0-] · Demandes par mois [nombre 0-]</t>
         </is>
       </c>
       <c r="R552" s="7" t="n"/>
@@ -39550,7 +39590,7 @@
       <c r="P554" s="7" t="n"/>
       <c r="Q554" s="6" t="inlineStr">
         <is>
-          <t>Clics [nombre] · Dépense [€ 0-] · Demandes [nombre]</t>
+          <t>Clics [nombre 0-] · Dépense [€ 0-] · Demandes [nombre 0-]</t>
         </is>
       </c>
       <c r="R554" s="6" t="inlineStr">

--- a/CAXE_Banque_Questions.xlsx
+++ b/CAXE_Banque_Questions.xlsx
@@ -39856,6 +39856,12 @@
           <t>%</t>
         </is>
       </c>
+      <c r="N558" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O558" s="6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="559">
       <c r="A559" s="6" t="inlineStr">
@@ -39891,7 +39897,7 @@
       </c>
       <c r="Q559" s="6" t="inlineStr">
         <is>
-          <t>Heures de production [heures] · Heures possibles [heures]</t>
+          <t>Heures de production [heures 0-] · Heures possibles [heures 0-]</t>
         </is>
       </c>
     </row>
@@ -39931,6 +39937,12 @@
         <is>
           <t>%</t>
         </is>
+      </c>
+      <c r="N560" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O560" s="6" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="561">
@@ -39963,7 +39975,7 @@
       </c>
       <c r="Q561" s="6" t="inlineStr">
         <is>
-          <t>Délai total [jours] · Dont attente avant lancement [jours]</t>
+          <t>Délai total [jours 0-] · Dont attente avant lancement [jours 0-]</t>
         </is>
       </c>
     </row>
@@ -40003,6 +40015,9 @@
         <is>
           <t>heures</t>
         </is>
+      </c>
+      <c r="N562" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
